--- a/sports_forms/009_football_trivia_quiz--sports_forms.xlsx
+++ b/sports_forms/009_football_trivia_quiz--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What year was the first football game played in England?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Football History</t>
+          <t>Who is the best football player of all time?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Football Teams</t>
+          <t>Which is the most successful football team?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Football Players</t>
+          <t>What is the biggest football stadium?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Football Stadiums</t>
+          <t>What is the Premier League?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Football Leagues</t>
+          <t>Who is Lionel Messi?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Football Dates</t>
+          <t>What is the current date?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Football Time</t>
+          <t>What time is it now?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Football Scores</t>
+          <t>How many goals did a player score in the last game?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Football Emails</t>
+          <t>What is the email address of a football club?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Football Phone</t>
+          <t>What is the phone number of a football club?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Football Address</t>
+          <t>What is the address of a football stadium?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Football Notes</t>
+          <t>Football Trivia Answer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Football Comments</t>
+          <t>Football Answer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Football Trivia</t>
+          <t>Football Question</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Football Trivia Answer</t>
+          <t>Football Trivia Quiz Page 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Football Answer</t>
+          <t>Football Trivia Quiz Page 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,172 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Football Result</t>
+          <t>Football Trivia Quiz Page 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>football_trivia_quiz_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Football Result</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,306 +965,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_2_choices</t>
+          <t>football_trivia_quiz_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_1':_'1892:_the_first_football_game_is_played_in_england'}</t>
+          <t>england_1892</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_1': '1892: The first football game is played in England'}</t>
+          <t>England 1892</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_2_choices</t>
+          <t>football_trivia_quiz_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_2':_'1894:_the_first_football_game_is_played_in_america'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_2': '1894: The first football game is played in America'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_2_choices</t>
+          <t>football_trivia_quiz_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_3':_'1896:_the_first_football_game_is_played_in_scotland'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_3': '1896: The first football game is played in Scotland'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_3_choices</t>
+          <t>football_trivia_quiz_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_1':_'manchester_united'}</t>
+          <t>cristiano_ronaldo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_1': 'Manchester United'}</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_3_choices</t>
+          <t>football_trivia_quiz_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_2':_'real_madrid'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_2': 'Real Madrid'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_3_choices</t>
+          <t>football_trivia_quiz_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option_3':_'liverpool'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option_3': 'Liverpool'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_4_choices</t>
+          <t>football_trivia_quiz_page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option_1':_'cristiano_ronaldo'}</t>
+          <t>manchester_united</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option_1': 'Cristiano Ronaldo'}</t>
+          <t>Manchester United</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_4_choices</t>
+          <t>football_trivia_quiz_page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option_2':_'lionel_messi'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option_2': 'Lionel Messi'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_4_choices</t>
+          <t>football_trivia_quiz_page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option_3':_'lionel_messi'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option_3': 'Lionel Messi'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_5_choices</t>
+          <t>football_trivia_quiz_page_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option_1':_'wembley'}</t>
+          <t>wembley</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option_1': 'Wembley'}</t>
+          <t>Wembley</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_5_choices</t>
+          <t>football_trivia_quiz_page_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option_2':_'celtic_park'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option_2': 'Celtic Park'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_5_choices</t>
+          <t>football_trivia_quiz_page_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option_3':_'old_trafford'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option_3': 'Old Trafford'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_6_choices</t>
+          <t>football_trivia_quiz_page_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option_1':_'premier_league'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option_1': 'Premier League'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_6_choices</t>
+          <t>football_trivia_quiz_page_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option_2':_'la_liga'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option_2': 'La Liga'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_6_choices</t>
+          <t>football_trivia_quiz_page_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option_3':_'champions_league'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option_3': 'Champions League'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_15_choices</t>
+          <t>football_trivia_quiz_page_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option_1':_'who_is_the_best_football_player_of_all_time?'}</t>
+          <t>lionel_messi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option_1': 'Who is the best football player of all time?'}</t>
+          <t>Lionel Messi</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>football_trivia_quiz_page_15_choices</t>
+          <t>football_trivia_quiz_page_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option_2':_'what_is_the_most_successful_football_team?'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option_2': 'What is the most successful football team?'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>football_trivia_quiz_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>football_trivia_quiz_page_15_choices</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'option_3':_'what_is_the_biggest_football_stadium?'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'option_3': 'What is the biggest football stadium?'}</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>football_trivia_quiz_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
